--- a/files/create_register_plan.xlsx
+++ b/files/create_register_plan.xlsx
@@ -1,142 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8CDE351-0B8C-4B79-B6B6-47796B91D388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C0B74D03-3A50-4E0B-A311-9572FD6ECA56}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
-  <si>
-    <t>LOGIN ID</t>
-  </si>
-  <si>
-    <t>PASSWORD</t>
-  </si>
-  <si>
-    <t>PR-DANGARPADA-V-ADM</t>
-  </si>
-  <si>
-    <t>Dang#1234</t>
-  </si>
-  <si>
-    <t>FINANCIAL YEAR1</t>
-  </si>
-  <si>
-    <t>FINANCIAL YEAR2</t>
-  </si>
-  <si>
-    <t>FINANCIAL YEAR3</t>
-  </si>
-  <si>
-    <t>FINANCIAL YEAR4</t>
-  </si>
-  <si>
-    <t>2023-2024</t>
-  </si>
-  <si>
-    <t>2024-2025</t>
-  </si>
-  <si>
-    <t>2025-2026</t>
-  </si>
-  <si>
-    <t>PR-HALDI-V-ADM</t>
-  </si>
-  <si>
-    <t>Hald#1234</t>
-  </si>
-  <si>
-    <t>PR-BITABANDH-V-ADM</t>
-  </si>
-  <si>
-    <t>zMf6GmSh</t>
-  </si>
-  <si>
-    <t>PR-TENTELKHUNTI-V-ADM</t>
-  </si>
-  <si>
-    <t>Tent#1234</t>
-  </si>
-  <si>
-    <t>PR-LEBEDA-V-ADM</t>
-  </si>
-  <si>
-    <t>Lebe#1234</t>
-  </si>
-  <si>
-    <t>PR-LAKHANA-V-ADM</t>
-  </si>
-  <si>
-    <t>Lakh#1234</t>
-  </si>
-  <si>
-    <t>Patr#1234</t>
-  </si>
-  <si>
-    <t>PR-PATRAPALIKHA-V-ADM</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+        <bgColor rgb="0092D050"/>
       </patternFill>
     </fill>
   </fills>
@@ -167,24 +78,86 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -504,159 +477,251 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{361F192D-950E-4256-9509-E9F9B93C06E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" customWidth="1"/>
+    <col width="22.21875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="19.33203125" customWidth="1" min="3" max="3"/>
+    <col width="13.77734375" customWidth="1" min="4" max="4"/>
+    <col width="15.5546875" customWidth="1" min="5" max="5"/>
+    <col width="14.21875" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LOGIN ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PASSWORD</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FINANCIAL YEAR1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FINANCIAL YEAR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FINANCIAL YEAR3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>FINANCIAL YEAR4</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>PR-DANGARPADA-V-ADM</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Dang#1234</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>PR-HALDI-V-ADM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Hald#1234</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PR-BITABANDH-V-ADM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>zMf6GmSh</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>PR-TENTELKHUNTI-V-ADM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tent#1234</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PR-LEBEDA-V-ADM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Lebe#1234</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PR-LAKHANA-V-ADM</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Lakh#1234</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PR-PATRAPALIKHA-V-ADM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Patr#1234</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>